--- a/scripts/libreria.xlsx
+++ b/scripts/libreria.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29922"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Superusuario\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADF4CAA-E677-4D4F-8154-C6B39915B15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="13960"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="89">
   <si>
     <t>Categoria</t>
   </si>
@@ -288,19 +292,19 @@
   </si>
   <si>
     <t>Single Vision CM3</t>
+  </si>
+  <si>
+    <t>Policarbonato Azul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV organic </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* \-??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,346 +333,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -706,263 +380,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -977,89 +406,158 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Coma" xfId="1" builtinId="3"/>
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
-    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
-    <cellStyle name="Coma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Moneda [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
-    <cellStyle name="Hipervínculo visitado" xfId="7" builtinId="9"/>
-    <cellStyle name="Nota" xfId="8" builtinId="10"/>
-    <cellStyle name="Texto de advertencia" xfId="9" builtinId="11"/>
-    <cellStyle name="Título" xfId="10" builtinId="15"/>
-    <cellStyle name="Texto explicativo" xfId="11" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
-    <cellStyle name="Salida" xfId="17" builtinId="21"/>
-    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
-    <cellStyle name="Celda de comprobación" xfId="19" builtinId="23"/>
-    <cellStyle name="Celda vinculada" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Correcto" xfId="22" builtinId="26"/>
-    <cellStyle name="Incorrecto" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
-    <cellStyle name="Énfasis1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Énfasis1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Énfasis1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Énfasis1" xfId="28" builtinId="32"/>
-    <cellStyle name="Énfasis2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Énfasis2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Énfasis2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Énfasis2" xfId="32" builtinId="36"/>
-    <cellStyle name="Énfasis3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Énfasis3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Énfasis3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Énfasis3" xfId="36" builtinId="40"/>
-    <cellStyle name="Énfasis4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Énfasis4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Énfasis4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Énfasis4" xfId="40" builtinId="44"/>
-    <cellStyle name="Énfasis5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Énfasis5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Énfasis5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Énfasis5" xfId="44" builtinId="48"/>
-    <cellStyle name="Énfasis6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Énfasis6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Énfasis6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Énfasis6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1070,7 +568,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1098,154 +596,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1503,22 +887,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I112"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I113"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.6171875" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.9375" customWidth="1"/>
-    <col min="4" max="4" width="21.734375" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.55" spans="1:4">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1532,7 +916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="17.55" spans="1:4">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1546,7 +930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="17.55" spans="1:4">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1560,7 +944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="17.55" spans="1:4">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1574,21 +958,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="17.55" spans="1:4">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="17.55" spans="1:4">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1602,7 +986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="17.55" spans="1:4">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1616,7 +1000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" ht="17.55" spans="1:4">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1630,7 +1014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="17.55" spans="1:4">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1644,7 +1028,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="17.55" spans="1:4">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1658,7 +1042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" ht="17.55" spans="1:4">
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -1672,7 +1056,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" ht="17.55" spans="1:4">
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -1686,7 +1070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" ht="17.55" spans="1:4">
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -1700,21 +1084,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" ht="17.55" spans="1:4">
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" ht="17.55" spans="1:4">
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -1728,7 +1112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" ht="17.55" spans="1:4">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -1742,21 +1126,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" ht="17.55" spans="1:4">
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" ht="17.55" spans="1:4">
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -1770,7 +1154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" ht="17.55" spans="1:4">
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -1784,7 +1168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" ht="17.55" spans="1:4">
+    <row r="20" spans="1:4" ht="25.5">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -1796,7 +1180,7 @@
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" ht="17.55" spans="1:4">
+    <row r="21" spans="1:4" ht="25.5">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -1808,7 +1192,7 @@
       </c>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" ht="17.55" spans="1:4">
+    <row r="22" spans="1:4" ht="25.5">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -1820,7 +1204,7 @@
       </c>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" ht="17.55" spans="1:3">
+    <row r="23" spans="1:4" ht="25.5">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -1831,7 +1215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" ht="17.55" spans="1:3">
+    <row r="24" spans="1:4" ht="25.5">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
@@ -1842,7 +1226,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" ht="17.55" spans="1:3">
+    <row r="25" spans="1:4" ht="25.5">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
@@ -1853,19 +1237,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" ht="17.55" spans="1:4">
+    <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>27</v>
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" ht="17.55" spans="1:4">
+    <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
@@ -1877,7 +1261,7 @@
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" ht="17.55" spans="1:4">
+    <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -1889,7 +1273,7 @@
       </c>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" ht="17.55" spans="1:4">
+    <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -1903,7 +1287,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" ht="17.55" spans="1:4">
+    <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
@@ -1917,7 +1301,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" ht="17.55" spans="1:4">
+    <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1931,21 +1315,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" ht="17.55" spans="1:4">
+    <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="33" ht="17.55" spans="1:4">
+    <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
         <v>30</v>
       </c>
@@ -1959,7 +1343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" ht="17.55" spans="1:4">
+    <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
         <v>30</v>
       </c>
@@ -1973,7 +1357,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" ht="17.55" spans="1:4">
+    <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1987,7 +1371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" ht="17.55" spans="1:4">
+    <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
         <v>30</v>
       </c>
@@ -2001,7 +1385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" ht="17.55" spans="1:4">
+    <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
         <v>30</v>
       </c>
@@ -2015,7 +1399,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" ht="17.55" spans="1:4">
+    <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
         <v>30</v>
       </c>
@@ -2029,7 +1413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" ht="17.55" spans="1:4">
+    <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
         <v>30</v>
       </c>
@@ -2043,7 +1427,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" ht="17.55" spans="1:4">
+    <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
         <v>30</v>
       </c>
@@ -2057,21 +1441,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" ht="17.55" spans="1:4">
+    <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" ht="17.55" spans="1:4">
+    <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
         <v>30</v>
       </c>
@@ -2085,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" ht="17.55" spans="1:4">
+    <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
         <v>30</v>
       </c>
@@ -2099,21 +1483,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" ht="17.55" spans="1:4">
+    <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" t="s">
         <v>34</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="45" ht="17.55" spans="1:4">
+    <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
         <v>30</v>
       </c>
@@ -2127,7 +1511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" ht="17.55" spans="1:4">
+    <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
         <v>30</v>
       </c>
@@ -2141,7 +1525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" ht="17.55" spans="1:4">
+    <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
         <v>30</v>
       </c>
@@ -2153,7 +1537,7 @@
       </c>
       <c r="D47" s="1"/>
     </row>
-    <row r="48" ht="17.55" spans="1:4">
+    <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
         <v>30</v>
       </c>
@@ -2165,7 +1549,7 @@
       </c>
       <c r="D48" s="1"/>
     </row>
-    <row r="49" ht="17.55" spans="1:4">
+    <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
         <v>30</v>
       </c>
@@ -2177,7 +1561,7 @@
       </c>
       <c r="D49" s="1"/>
     </row>
-    <row r="50" ht="17.55" spans="1:3">
+    <row r="50" spans="1:8" ht="25.5">
       <c r="A50" s="1" t="s">
         <v>30</v>
       </c>
@@ -2188,7 +1572,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" ht="17.55" spans="1:3">
+    <row r="51" spans="1:8" ht="25.5">
       <c r="A51" s="1" t="s">
         <v>30</v>
       </c>
@@ -2199,7 +1583,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" ht="17.55" spans="1:3">
+    <row r="52" spans="1:8" ht="25.5">
       <c r="A52" s="1" t="s">
         <v>30</v>
       </c>
@@ -2210,19 +1594,19 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" ht="17.55" spans="1:4">
+    <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" t="s">
         <v>43</v>
       </c>
       <c r="D53" s="1"/>
     </row>
-    <row r="54" ht="17.55" spans="1:4">
+    <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
         <v>30</v>
       </c>
@@ -2234,7 +1618,7 @@
       </c>
       <c r="D54" s="1"/>
     </row>
-    <row r="55" ht="17.55" spans="1:4">
+    <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
         <v>30</v>
       </c>
@@ -2246,7 +1630,7 @@
       </c>
       <c r="D55" s="1"/>
     </row>
-    <row r="56" ht="17.55" spans="1:4">
+    <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
         <v>46</v>
       </c>
@@ -2258,7 +1642,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="57" ht="17.55" spans="1:4">
+    <row r="57" spans="1:8" ht="25.5">
       <c r="A57" s="1" t="s">
         <v>46</v>
       </c>
@@ -2270,7 +1654,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" ht="17.55" spans="1:4">
+    <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
         <v>46</v>
       </c>
@@ -2282,7 +1666,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" ht="17.55" spans="1:8">
+    <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
         <v>50</v>
       </c>
@@ -2295,11 +1679,11 @@
       <c r="D59" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" ht="17.55" spans="1:8">
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
         <v>50</v>
       </c>
@@ -2310,11 +1694,11 @@
         <v>54</v>
       </c>
       <c r="D60" s="1"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" ht="17.55" spans="1:8">
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
         <v>50</v>
       </c>
@@ -2325,11 +1709,11 @@
         <v>55</v>
       </c>
       <c r="D61" s="1"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-    </row>
-    <row r="62" ht="18.3" spans="1:8">
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
         <v>50</v>
       </c>
@@ -2340,11 +1724,11 @@
         <v>56</v>
       </c>
       <c r="D62" s="1"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-    </row>
-    <row r="63" ht="17.55" spans="1:4">
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
         <v>50</v>
       </c>
@@ -2356,7 +1740,7 @@
       </c>
       <c r="D63" s="1"/>
     </row>
-    <row r="64" ht="17.55" spans="1:4">
+    <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
         <v>50</v>
       </c>
@@ -2368,7 +1752,7 @@
       </c>
       <c r="D64" s="1"/>
     </row>
-    <row r="65" ht="17.55" spans="1:4">
+    <row r="65" spans="1:4">
       <c r="A65" s="1" t="s">
         <v>50</v>
       </c>
@@ -2380,7 +1764,7 @@
       </c>
       <c r="D65" s="1"/>
     </row>
-    <row r="66" ht="17.55" spans="1:4">
+    <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
         <v>50</v>
       </c>
@@ -2392,7 +1776,7 @@
       </c>
       <c r="D66" s="1"/>
     </row>
-    <row r="67" ht="17.55" spans="1:4">
+    <row r="67" spans="1:4">
       <c r="A67" s="1" t="s">
         <v>50</v>
       </c>
@@ -2404,7 +1788,7 @@
       </c>
       <c r="D67" s="1"/>
     </row>
-    <row r="68" ht="17.55" spans="1:4">
+    <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
         <v>50</v>
       </c>
@@ -2416,7 +1800,7 @@
       </c>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" ht="29.75" spans="1:4">
+    <row r="69" spans="1:4" ht="25.5">
       <c r="A69" s="1" t="s">
         <v>50</v>
       </c>
@@ -2428,7 +1812,7 @@
       </c>
       <c r="D69" s="1"/>
     </row>
-    <row r="70" ht="17.55" spans="1:4">
+    <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
         <v>50</v>
       </c>
@@ -2440,7 +1824,7 @@
       </c>
       <c r="D70" s="1"/>
     </row>
-    <row r="71" ht="17.55" spans="1:4">
+    <row r="71" spans="1:4">
       <c r="A71" s="1" t="s">
         <v>50</v>
       </c>
@@ -2452,7 +1836,7 @@
       </c>
       <c r="D71" s="1"/>
     </row>
-    <row r="72" ht="17.55" spans="1:4">
+    <row r="72" spans="1:4">
       <c r="A72" s="1" t="s">
         <v>50</v>
       </c>
@@ -2466,7 +1850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" ht="17.55" spans="1:4">
+    <row r="73" spans="1:4">
       <c r="A73" s="1" t="s">
         <v>50</v>
       </c>
@@ -2480,7 +1864,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" ht="17.55" spans="1:4">
+    <row r="74" spans="1:4">
       <c r="A74" s="1" t="s">
         <v>50</v>
       </c>
@@ -2494,7 +1878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" ht="17.55" spans="1:4">
+    <row r="75" spans="1:4">
       <c r="A75" s="1" t="s">
         <v>50</v>
       </c>
@@ -2508,7 +1892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" ht="17.55" spans="1:4">
+    <row r="76" spans="1:4">
       <c r="A76" s="1" t="s">
         <v>50</v>
       </c>
@@ -2522,7 +1906,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" ht="17.55" spans="1:4">
+    <row r="77" spans="1:4" ht="25.5">
       <c r="A77" s="1" t="s">
         <v>50</v>
       </c>
@@ -2534,35 +1918,35 @@
       </c>
       <c r="D77" s="1"/>
     </row>
-    <row r="78" ht="17.55" spans="1:4">
+    <row r="78" spans="1:4">
       <c r="A78" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="79" ht="17.55" spans="1:4">
+    <row r="79" spans="1:4">
       <c r="A79" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="80" ht="17.55" spans="1:4">
+    <row r="80" spans="1:4">
       <c r="A80" s="1" t="s">
         <v>50</v>
       </c>
@@ -2570,13 +1954,13 @@
         <v>72</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:7">
       <c r="A81" s="1" t="s">
         <v>50</v>
       </c>
@@ -2584,82 +1968,81 @@
         <v>72</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D81" s="1"/>
-    </row>
-    <row r="82" ht="17.55" spans="1:4">
-      <c r="A82" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D82" s="1"/>
-    </row>
-    <row r="83" ht="17.55" spans="1:6">
+      <c r="D82" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F83" s="3"/>
-    </row>
-    <row r="84" ht="17.55" spans="1:6">
+        <v>72</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D83" s="1"/>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D84" s="1"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F84" s="3"/>
-    </row>
-    <row r="85" ht="18.3" spans="1:6">
-      <c r="A85" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F85" s="4"/>
-    </row>
-    <row r="86" ht="17.55" spans="1:4">
+      <c r="F85" s="2"/>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="87" ht="17.55" spans="1:4">
+      <c r="F86" s="2"/>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" s="1" t="s">
         <v>50</v>
       </c>
@@ -2667,13 +2050,14 @@
         <v>72</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" ht="17.55" spans="1:4">
+        <v>74</v>
+      </c>
+      <c r="F87" s="3"/>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" s="1" t="s">
         <v>50</v>
       </c>
@@ -2681,13 +2065,13 @@
         <v>72</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="89" ht="17.55" spans="1:4">
+    <row r="89" spans="1:7">
       <c r="A89" s="1" t="s">
         <v>50</v>
       </c>
@@ -2695,51 +2079,53 @@
         <v>72</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="90" ht="17.55" spans="1:4">
+    <row r="90" spans="1:7">
       <c r="A90" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C90" s="1"/>
+        <v>72</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="D90" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="91" ht="17.55" spans="1:4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D91" s="1"/>
-    </row>
-    <row r="92" ht="17.55" spans="1:4">
+        <v>55</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="C92" s="1"/>
       <c r="D92" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" ht="17.55" spans="1:4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" s="1" t="s">
         <v>50</v>
       </c>
@@ -2747,13 +2133,11 @@
         <v>26</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D93" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="94" ht="18.3" spans="1:7">
+      <c r="D93" s="1"/>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" s="1" t="s">
         <v>50</v>
       </c>
@@ -2764,12 +2148,10 @@
         <v>81</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-    </row>
-    <row r="95" ht="17.55" spans="1:4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" s="1" t="s">
         <v>50</v>
       </c>
@@ -2777,11 +2159,13 @@
         <v>26</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D95" s="1"/>
-    </row>
-    <row r="96" ht="17.55" spans="1:4">
+        <v>82</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" s="1" t="s">
         <v>50</v>
       </c>
@@ -2789,72 +2173,96 @@
         <v>26</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D96" s="1"/>
-    </row>
-    <row r="97" ht="17.55" spans="1:4">
+        <v>81</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1" t="s">
+      <c r="C97" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D97" s="1"/>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D98" s="1"/>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="98" ht="17.55" spans="1:4">
-      <c r="A98" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B98" s="1" t="s">
+    <row r="100" spans="1:9">
+      <c r="A100" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1" t="s">
+      <c r="C100" s="1"/>
+      <c r="D100" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="99" ht="17.55" spans="1:4">
-      <c r="A99" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B99" s="1" t="s">
+    <row r="101" spans="1:9">
+      <c r="A101" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C101" t="s">
         <v>86</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D101" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="100" ht="17.55" spans="1:2">
-      <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
-    </row>
-    <row r="105" ht="17.55"/>
-    <row r="106" ht="18.3" spans="9:9">
-      <c r="I106" s="4"/>
-    </row>
-    <row r="107" ht="17.55"/>
-    <row r="108" spans="8:8">
-      <c r="H108" s="6"/>
-    </row>
-    <row r="109" spans="8:8">
-      <c r="H109" s="6"/>
-    </row>
-    <row r="110" ht="17.55" spans="8:8">
-      <c r="H110" s="6"/>
-    </row>
-    <row r="111" ht="18.3" spans="8:8">
-      <c r="H111" s="4"/>
-    </row>
-    <row r="112" ht="17.55"/>
+    <row r="102" spans="1:9">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="I108" s="3"/>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="H110" s="5"/>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="H111" s="5"/>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="H112" s="5"/>
+    </row>
+    <row r="113" spans="8:8">
+      <c r="H113" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/scripts/libreria.xlsx
+++ b/scripts/libreria.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Superusuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Superusuario\Documents\dashboard-rodenstock\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADF4CAA-E677-4D4F-8154-C6B39915B15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D70E8C-2DA1-488A-92D5-1CFD2067700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="90">
   <si>
     <t>Categoria</t>
   </si>
@@ -298,13 +298,16 @@
   </si>
   <si>
     <t xml:space="preserve">SV organic </t>
+  </si>
+  <si>
+    <t>Single Vision 1.60</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +334,20 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -386,7 +403,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -403,6 +420,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -1752,7 +1775,7 @@
       </c>
       <c r="D64" s="1"/>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:6">
       <c r="A65" s="1" t="s">
         <v>50</v>
       </c>
@@ -1764,7 +1787,7 @@
       </c>
       <c r="D65" s="1"/>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:6">
       <c r="A66" s="1" t="s">
         <v>50</v>
       </c>
@@ -1776,7 +1799,7 @@
       </c>
       <c r="D66" s="1"/>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:6">
       <c r="A67" s="1" t="s">
         <v>50</v>
       </c>
@@ -1788,7 +1811,7 @@
       </c>
       <c r="D67" s="1"/>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:6">
       <c r="A68" s="1" t="s">
         <v>50</v>
       </c>
@@ -1800,7 +1823,7 @@
       </c>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="1:4" ht="25.5">
+    <row r="69" spans="1:6" ht="25.5">
       <c r="A69" s="1" t="s">
         <v>50</v>
       </c>
@@ -1812,7 +1835,7 @@
       </c>
       <c r="D69" s="1"/>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:6">
       <c r="A70" s="1" t="s">
         <v>50</v>
       </c>
@@ -1824,7 +1847,7 @@
       </c>
       <c r="D70" s="1"/>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:6">
       <c r="A71" s="1" t="s">
         <v>50</v>
       </c>
@@ -1836,7 +1859,7 @@
       </c>
       <c r="D71" s="1"/>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:6">
       <c r="A72" s="1" t="s">
         <v>50</v>
       </c>
@@ -1850,7 +1873,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:6">
       <c r="A73" s="1" t="s">
         <v>50</v>
       </c>
@@ -1864,7 +1887,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:6">
       <c r="A74" s="1" t="s">
         <v>50</v>
       </c>
@@ -1878,7 +1901,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:6">
       <c r="A75" s="1" t="s">
         <v>50</v>
       </c>
@@ -1892,7 +1915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:6">
       <c r="A76" s="1" t="s">
         <v>50</v>
       </c>
@@ -1906,7 +1929,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="25.5">
+    <row r="77" spans="1:6" ht="26.25" thickBot="1">
       <c r="A77" s="1" t="s">
         <v>50</v>
       </c>
@@ -1917,64 +1940,65 @@
         <v>73</v>
       </c>
       <c r="D77" s="1"/>
-    </row>
-    <row r="78" spans="1:4">
+      <c r="F77" s="7"/>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" thickBot="1">
       <c r="A78" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>58</v>
+      <c r="C78" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" thickBot="1">
       <c r="A79" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A80" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:6">
       <c r="A81" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:6">
       <c r="A82" s="1" t="s">
         <v>50</v>
       </c>
@@ -1982,13 +2006,13 @@
         <v>72</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:6">
       <c r="A83" s="1" t="s">
         <v>50</v>
       </c>
@@ -1996,82 +2020,81 @@
         <v>72</v>
       </c>
       <c r="C83" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D83" s="1"/>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D84" s="1"/>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="D84" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F85" s="2"/>
-    </row>
-    <row r="86" spans="1:7">
+        <v>72</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D85" s="1"/>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D86" s="1"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F86" s="2"/>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F87" s="3"/>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="F87" s="2"/>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="89" spans="1:7">
+      <c r="F88" s="2"/>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" s="1" t="s">
         <v>50</v>
       </c>
@@ -2079,13 +2102,14 @@
         <v>72</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>74</v>
+      </c>
+      <c r="F89" s="3"/>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="1" t="s">
         <v>50</v>
       </c>
@@ -2093,13 +2117,13 @@
         <v>72</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:6">
       <c r="A91" s="1" t="s">
         <v>50</v>
       </c>
@@ -2107,51 +2131,53 @@
         <v>72</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:6">
       <c r="A92" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C92" s="1"/>
+        <v>72</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="D92" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D93" s="1"/>
-    </row>
-    <row r="94" spans="1:7">
+        <v>55</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="1" t="s">
         <v>50</v>
       </c>
@@ -2159,13 +2185,11 @@
         <v>26</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D95" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="96" spans="1:7">
+      <c r="D95" s="1"/>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="1" t="s">
         <v>50</v>
       </c>
@@ -2176,10 +2200,8 @@
         <v>81</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="1" t="s">
@@ -2189,9 +2211,11 @@
         <v>26</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D97" s="1"/>
+        <v>82</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="1" t="s">
@@ -2201,9 +2225,13 @@
         <v>26</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D98" s="1"/>
+        <v>81</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="1" t="s">
@@ -2212,57 +2240,82 @@
       <c r="B99" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="C99" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D99" s="1"/>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1" t="s">
-        <v>85</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D100" s="1"/>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C102" s="1"/>
+      <c r="D102" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" t="s">
         <v>86</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
-      <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
-    </row>
-    <row r="108" spans="1:9">
-      <c r="I108" s="3"/>
+    <row r="104" spans="1:9">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
     </row>
     <row r="110" spans="1:9">
-      <c r="H110" s="5"/>
-    </row>
-    <row r="111" spans="1:9">
-      <c r="H111" s="5"/>
+      <c r="I110" s="3"/>
     </row>
     <row r="112" spans="1:9">
       <c r="H112" s="5"/>
     </row>
     <row r="113" spans="8:8">
-      <c r="H113" s="3"/>
+      <c r="H113" s="5"/>
+    </row>
+    <row r="114" spans="8:8">
+      <c r="H114" s="5"/>
+    </row>
+    <row r="115" spans="8:8">
+      <c r="H115" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/scripts/libreria.xlsx
+++ b/scripts/libreria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Superusuario\Documents\dashboard-rodenstock\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D70E8C-2DA1-488A-92D5-1CFD2067700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35E5BF8-9463-4DB5-9BEA-43D438D04BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,36 +319,29 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF202124"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -359,42 +352,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF0C67DF"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF0C67DF"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF0C67DF"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF0C67DF"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -403,29 +366,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -917,12 +877,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22" style="2" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -988,7 +949,7 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1114,7 +1075,7 @@
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1156,7 +1117,7 @@
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1267,7 +1228,7 @@
       <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D26" s="1"/>
@@ -1345,7 +1306,7 @@
       <c r="B32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -1471,7 +1432,7 @@
       <c r="B41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -1513,7 +1474,7 @@
       <c r="B44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -1624,7 +1585,7 @@
       <c r="B53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D53" s="1"/>
@@ -1702,9 +1663,9 @@
       <c r="D59" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
@@ -1717,9 +1678,9 @@
         <v>54</v>
       </c>
       <c r="D60" s="1"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
@@ -1732,9 +1693,9 @@
         <v>55</v>
       </c>
       <c r="D61" s="1"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
@@ -1929,7 +1890,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="26.25" thickBot="1">
+    <row r="77" spans="1:6" ht="25.5">
       <c r="A77" s="1" t="s">
         <v>50</v>
       </c>
@@ -1940,37 +1901,37 @@
         <v>73</v>
       </c>
       <c r="D77" s="1"/>
-      <c r="F77" s="7"/>
-    </row>
-    <row r="78" spans="1:6" ht="15.75" thickBot="1">
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="5" t="s">
         <v>89</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15.75" thickBot="1">
+    <row r="79" spans="1:6">
       <c r="A79" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="5" t="s">
         <v>89</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="15.75" thickBot="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="1" t="s">
         <v>50</v>
       </c>
@@ -2071,13 +2032,13 @@
       <c r="B87" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F87" s="2"/>
+      <c r="F87" s="3"/>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">
@@ -2086,13 +2047,13 @@
       <c r="B88" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F88" s="2"/>
+      <c r="F88" s="3"/>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="1" t="s">
@@ -2288,7 +2249,7 @@
       <c r="B103" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -2303,13 +2264,13 @@
       <c r="I110" s="3"/>
     </row>
     <row r="112" spans="1:9">
-      <c r="H112" s="5"/>
+      <c r="H112" s="6"/>
     </row>
     <row r="113" spans="8:8">
-      <c r="H113" s="5"/>
+      <c r="H113" s="6"/>
     </row>
     <row r="114" spans="8:8">
-      <c r="H114" s="5"/>
+      <c r="H114" s="6"/>
     </row>
     <row r="115" spans="8:8">
       <c r="H115" s="3"/>
